--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="M57" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="N57" t="n">
-        <v>3.69</v>
+        <v>5.01</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,17 +7676,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8477,22 +8477,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8509,17 +8509,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.41</v>
+        <v>5.28</v>
       </c>
       <c r="M112" t="n">
-        <v>5.23</v>
+        <v>4.67</v>
       </c>
       <c r="N112" t="n">
-        <v>8.6</v>
+        <v>1.64</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="N113" t="n">
-        <v>5.18</v>
+        <v>4.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="M114" t="n">
-        <v>4.55</v>
+        <v>5.23</v>
       </c>
       <c r="N114" t="n">
-        <v>4.85</v>
+        <v>8.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.28</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>4.67</v>
+        <v>4.17</v>
       </c>
       <c r="N115" t="n">
-        <v>1.64</v>
+        <v>5.18</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.76</v>
+        <v>3.76</v>
       </c>
       <c r="M123" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="N123" t="n">
-        <v>4.17</v>
+        <v>2.07</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="M136" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="N136" t="n">
-        <v>5.91</v>
+        <v>2.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29457,13 +29457,13 @@
         </is>
       </c>
       <c r="L244" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M244" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N244" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
         <v>0</v>
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N277" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M283" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N283" t="n">
-        <v>3.77</v>
+        <v>4.76</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34137,10 +34137,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,10 +34256,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L293" t="n">
@@ -35371,22 +35371,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -35490,22 +35490,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G295" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="M55" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="N55" t="n">
-        <v>3.69</v>
+        <v>3.03</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,22 +7644,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7676,17 +7676,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9104,17 +9104,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M112" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N112" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>5.28</v>
       </c>
       <c r="M113" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="N113" t="n">
-        <v>4.85</v>
+        <v>1.64</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N114" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.01</v>
+        <v>3.07</v>
       </c>
       <c r="M116" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="N116" t="n">
-        <v>3.46</v>
+        <v>2.52</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,22 +15379,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.48</v>
+        <v>12</v>
       </c>
       <c r="M138" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="N138" t="n">
-        <v>6.51</v>
+        <v>1.22</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="M151" t="n">
-        <v>5.05</v>
+        <v>3.34</v>
       </c>
       <c r="N151" t="n">
-        <v>1.29</v>
+        <v>2.68</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22124,10 +22124,10 @@
         <v>0</v>
       </c>
       <c r="AA182" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB182" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,22 +24066,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,22 +24661,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,22 +25256,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="M223" t="n">
-        <v>3.72</v>
+        <v>5.68</v>
       </c>
       <c r="N223" t="n">
-        <v>3.6</v>
+        <v>14.2</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N243" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31769,10 +31769,10 @@
         <v>0</v>
       </c>
       <c r="AC263" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD263" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32007,10 +32007,10 @@
         <v>0</v>
       </c>
       <c r="AC265" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD265" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE265" t="n">
         <v>0</v>
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="M283" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="N283" t="n">
-        <v>4.76</v>
+        <v>3.57</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34137,10 +34137,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L293" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -35728,22 +35728,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35976,12 +35976,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -37047,12 +37047,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -37166,12 +37166,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G309" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,22 +5264,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,22 +7406,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,22 +7763,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7795,17 +7795,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,22 +9072,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9104,17 +9104,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="M112" t="n">
-        <v>5.23</v>
+        <v>4.17</v>
       </c>
       <c r="N112" t="n">
-        <v>8.6</v>
+        <v>5.18</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,16 +13794,16 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M113" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N113" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.7</v>
+        <v>5.28</v>
       </c>
       <c r="M114" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="N114" t="n">
-        <v>4.85</v>
+        <v>1.64</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="M115" t="n">
-        <v>4.17</v>
+        <v>4.55</v>
       </c>
       <c r="N115" t="n">
-        <v>5.18</v>
+        <v>4.85</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>3.07</v>
+        <v>12</v>
       </c>
       <c r="M116" t="n">
-        <v>3.42</v>
+        <v>6.1</v>
       </c>
       <c r="N116" t="n">
-        <v>2.52</v>
+        <v>1.22</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.95</v>
+        <v>4.3</v>
       </c>
       <c r="M143" t="n">
-        <v>3.48</v>
+        <v>4.3</v>
       </c>
       <c r="N143" t="n">
-        <v>3.74</v>
+        <v>1.72</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="M146" t="n">
-        <v>4.4</v>
+        <v>3.48</v>
       </c>
       <c r="N146" t="n">
-        <v>5.91</v>
+        <v>3.74</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="M156" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="N156" t="n">
-        <v>4.17</v>
+        <v>2.83</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22194,17 +22194,17 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M183" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB183" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,22 +24661,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="M224" t="n">
-        <v>3.72</v>
+        <v>5.68</v>
       </c>
       <c r="N224" t="n">
-        <v>3.6</v>
+        <v>14.2</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB224" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="M229" t="n">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="N229" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="M241" t="n">
-        <v>4.73</v>
+        <v>3.15</v>
       </c>
       <c r="N241" t="n">
-        <v>5.91</v>
+        <v>4.42</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -29312,12 +29312,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31412,10 +31412,10 @@
         <v>0</v>
       </c>
       <c r="AC260" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD260" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31920,7 +31920,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32007,10 +32007,10 @@
         <v>0</v>
       </c>
       <c r="AC265" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD265" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE265" t="n">
         <v>0</v>
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M282" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="N282" t="n">
-        <v>4.76</v>
+        <v>3.77</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M283" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N283" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M284" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N284" t="n">
-        <v>3.77</v>
+        <v>4.76</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,10 +34256,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB289" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -34976,10 +34976,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
         <v>0</v>
@@ -35014,22 +35014,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35284,7 +35284,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L293" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35728,22 +35728,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35966,22 +35966,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -37047,12 +37047,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -37166,12 +37166,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G309" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="M53" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>5.01</v>
+        <v>2.57</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,22 +6811,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,22 +7763,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7795,17 +7795,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8033,17 +8033,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,22 +11095,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.72</v>
+        <v>5.28</v>
       </c>
       <c r="M112" t="n">
-        <v>4.17</v>
+        <v>4.67</v>
       </c>
       <c r="N112" t="n">
-        <v>5.18</v>
+        <v>1.64</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13794,16 +13794,16 @@
         <v>0</v>
       </c>
       <c r="AA112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N113" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>5.28</v>
+        <v>1.72</v>
       </c>
       <c r="M114" t="n">
-        <v>4.67</v>
+        <v>4.17</v>
       </c>
       <c r="N114" t="n">
-        <v>1.64</v>
+        <v>5.18</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,16 +14032,16 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="M115" t="n">
-        <v>4.55</v>
+        <v>5.23</v>
       </c>
       <c r="N115" t="n">
-        <v>4.85</v>
+        <v>8.6</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>12</v>
+        <v>1.95</v>
       </c>
       <c r="M116" t="n">
-        <v>6.1</v>
+        <v>3.48</v>
       </c>
       <c r="N116" t="n">
-        <v>1.22</v>
+        <v>3.74</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="M118" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="N118" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="M119" t="n">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="N119" t="n">
-        <v>4.17</v>
+        <v>2.68</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.07</v>
+        <v>3.76</v>
       </c>
       <c r="M142" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="N142" t="n">
-        <v>2.52</v>
+        <v>2.07</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.31</v>
+        <v>1.76</v>
       </c>
       <c r="M156" t="n">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="N156" t="n">
-        <v>2.83</v>
+        <v>4.17</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22198,13 +22198,13 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N183" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O183" t="n">
         <v>0</v>
@@ -22243,10 +22243,10 @@
         <v>0</v>
       </c>
       <c r="AA183" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB183" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC183" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22789,7 +22789,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L188" t="n">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="M208" t="n">
-        <v>2.74</v>
+        <v>3.43</v>
       </c>
       <c r="N208" t="n">
-        <v>3.74</v>
+        <v>2.01</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,22 +6573,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>3.03</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="M59" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="N59" t="n">
-        <v>3.69</v>
+        <v>5.01</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8033,17 +8033,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,22 +8120,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>5.28</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>4.67</v>
+        <v>4.55</v>
       </c>
       <c r="N112" t="n">
-        <v>1.64</v>
+        <v>4.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="M113" t="n">
-        <v>4.55</v>
+        <v>5.23</v>
       </c>
       <c r="N113" t="n">
-        <v>4.85</v>
+        <v>8.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.41</v>
+        <v>5.28</v>
       </c>
       <c r="M115" t="n">
-        <v>5.23</v>
+        <v>4.67</v>
       </c>
       <c r="N115" t="n">
-        <v>8.6</v>
+        <v>1.64</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.95</v>
+        <v>2.43</v>
       </c>
       <c r="M116" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="N116" t="n">
-        <v>3.74</v>
+        <v>2.75</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,22 +16450,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.01</v>
+        <v>2.31</v>
       </c>
       <c r="M139" t="n">
         <v>3.56</v>
       </c>
       <c r="N139" t="n">
-        <v>3.46</v>
+        <v>2.83</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.76</v>
+        <v>2.25</v>
       </c>
       <c r="M142" t="n">
-        <v>3.76</v>
+        <v>3.11</v>
       </c>
       <c r="N142" t="n">
-        <v>2.07</v>
+        <v>3.05</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB153" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.76</v>
+        <v>12</v>
       </c>
       <c r="M156" t="n">
-        <v>3.88</v>
+        <v>6.1</v>
       </c>
       <c r="N156" t="n">
-        <v>4.17</v>
+        <v>1.22</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.48</v>
+        <v>2.17</v>
       </c>
       <c r="M163" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="N163" t="n">
-        <v>6.51</v>
+        <v>3.13</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB179" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,22 +23947,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="M203" t="n">
-        <v>2.74</v>
+        <v>3.89</v>
       </c>
       <c r="N203" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,22 +24661,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.01</v>
+        <v>1.85</v>
       </c>
       <c r="M220" t="n">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
       <c r="N220" t="n">
-        <v>2.66</v>
+        <v>3.7</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="M225" t="n">
-        <v>3.72</v>
+        <v>5.68</v>
       </c>
       <c r="N225" t="n">
-        <v>3.6</v>
+        <v>14.2</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>1.85</v>
+        <v>3.01</v>
       </c>
       <c r="M226" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="N226" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="M229" t="n">
-        <v>3.31</v>
+        <v>2.97</v>
       </c>
       <c r="N229" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,22 +28707,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -29550,12 +29550,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,61 +31242,61 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>5.5</v>
+        <v>5.03</v>
       </c>
       <c r="M259" t="n">
-        <v>3.96</v>
+        <v>4.62</v>
       </c>
       <c r="N259" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>0</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
+      <c r="S259" t="n">
+        <v>0</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0</v>
+      </c>
+      <c r="U259" t="n">
+        <v>0</v>
+      </c>
+      <c r="V259" t="n">
+        <v>0</v>
+      </c>
+      <c r="W259" t="n">
+        <v>0</v>
+      </c>
+      <c r="X259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD259" t="n">
         <v>1.58</v>
-      </c>
-      <c r="O259" t="n">
-        <v>0</v>
-      </c>
-      <c r="P259" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
-      <c r="R259" t="n">
-        <v>0</v>
-      </c>
-      <c r="S259" t="n">
-        <v>0</v>
-      </c>
-      <c r="T259" t="n">
-        <v>0</v>
-      </c>
-      <c r="U259" t="n">
-        <v>0</v>
-      </c>
-      <c r="V259" t="n">
-        <v>0</v>
-      </c>
-      <c r="W259" t="n">
-        <v>0</v>
-      </c>
-      <c r="X259" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y259" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z259" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA259" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB259" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC259" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD259" t="n">
-        <v>0</v>
       </c>
       <c r="AE259" t="n">
         <v>0</v>
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="M260" t="n">
-        <v>4.62</v>
+        <v>3.96</v>
       </c>
       <c r="N260" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,16 +31406,16 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC260" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD260" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="M281" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="N281" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M282" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N282" t="n">
-        <v>3.77</v>
+        <v>4.76</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M284" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N284" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,10 +34256,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,22 +35014,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35371,22 +35371,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35728,22 +35728,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L297" t="n">
@@ -35847,22 +35847,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35966,22 +35966,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -37047,12 +37047,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -37156,7 +37156,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -37166,12 +37166,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G309" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>2.21</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>6.19</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,22 +6573,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="M54" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="M59" t="n">
-        <v>4.25</v>
+        <v>3.37</v>
       </c>
       <c r="N59" t="n">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,22 +8120,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.9</v>
+        <v>1.93</v>
       </c>
       <c r="M65" t="n">
-        <v>5.39</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>1.45</v>
+        <v>4.23</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>5.28</v>
       </c>
       <c r="M112" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="N112" t="n">
-        <v>4.85</v>
+        <v>1.64</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N113" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="M114" t="n">
-        <v>4.17</v>
+        <v>5.23</v>
       </c>
       <c r="N114" t="n">
-        <v>5.18</v>
+        <v>8.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,16 +14032,16 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.28</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>4.67</v>
+        <v>4.17</v>
       </c>
       <c r="N115" t="n">
-        <v>1.64</v>
+        <v>5.18</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="M116" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="N116" t="n">
-        <v>2.75</v>
+        <v>3.74</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>10.6</v>
+        <v>2.5</v>
       </c>
       <c r="M127" t="n">
-        <v>5.05</v>
+        <v>3.34</v>
       </c>
       <c r="N127" t="n">
-        <v>1.29</v>
+        <v>2.68</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.48</v>
+        <v>12</v>
       </c>
       <c r="M130" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="N130" t="n">
-        <v>6.51</v>
+        <v>1.22</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M138" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.76</v>
+        <v>1.49</v>
       </c>
       <c r="M146" t="n">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
       <c r="N146" t="n">
-        <v>2.07</v>
+        <v>5.91</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.51</v>
+        <v>1.37</v>
       </c>
       <c r="M149" t="n">
-        <v>3.12</v>
+        <v>4.56</v>
       </c>
       <c r="N149" t="n">
-        <v>2.66</v>
+        <v>6.47</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18673,10 +18673,10 @@
         <v>0</v>
       </c>
       <c r="AA153" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB153" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>12</v>
+        <v>2.61</v>
       </c>
       <c r="M156" t="n">
-        <v>6.1</v>
+        <v>3.24</v>
       </c>
       <c r="N156" t="n">
-        <v>1.22</v>
+        <v>2.47</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.01</v>
+        <v>1.76</v>
       </c>
       <c r="M159" t="n">
-        <v>3.56</v>
+        <v>3.88</v>
       </c>
       <c r="N159" t="n">
-        <v>3.46</v>
+        <v>4.17</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,22 +24542,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="M203" t="n">
-        <v>3.89</v>
+        <v>4.11</v>
       </c>
       <c r="N203" t="n">
-        <v>3.01</v>
+        <v>8.01</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,22 +24661,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>5.34</v>
+        <v>1.3</v>
       </c>
       <c r="M218" t="n">
-        <v>3.38</v>
+        <v>5.68</v>
       </c>
       <c r="N218" t="n">
-        <v>1.71</v>
+        <v>14.2</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.13</v>
+        <v>3.01</v>
       </c>
       <c r="M223" t="n">
-        <v>3.72</v>
+        <v>3.26</v>
       </c>
       <c r="N223" t="n">
-        <v>3.6</v>
+        <v>2.66</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="M225" t="n">
-        <v>5.68</v>
+        <v>3.72</v>
       </c>
       <c r="N225" t="n">
-        <v>14.2</v>
+        <v>3.6</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>3.01</v>
+        <v>5.34</v>
       </c>
       <c r="M226" t="n">
-        <v>3.26</v>
+        <v>3.38</v>
       </c>
       <c r="N226" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="M229" t="n">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="N229" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="M230" t="n">
-        <v>3.31</v>
+        <v>2.97</v>
       </c>
       <c r="N230" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,22 +28707,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,22 +28826,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="M258" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N258" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N259" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31293,10 +31293,10 @@
         <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD259" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE259" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32126,10 +32126,10 @@
         <v>0</v>
       </c>
       <c r="AC266" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD266" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N278" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="M280" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="N280" t="n">
-        <v>3.57</v>
+        <v>3.77</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M281" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N281" t="n">
-        <v>3.77</v>
+        <v>4.76</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33899,10 +33899,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z281" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M284" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB285" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N287" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35252,22 +35252,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35609,7 +35609,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35728,7 +35728,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35760,7 +35760,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L297" t="n">
@@ -35847,7 +35847,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35879,7 +35879,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -35966,22 +35966,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36918,7 +36918,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -36928,12 +36928,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -37037,7 +37037,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -37047,12 +37047,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -37166,12 +37166,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G309" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI310"/>
+  <dimension ref="A1:AI306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,22 +4193,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,22 +5383,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.34</v>
+        <v>1.84</v>
       </c>
       <c r="M51" t="n">
-        <v>3.22</v>
+        <v>3.95</v>
       </c>
       <c r="N51" t="n">
-        <v>3.03</v>
+        <v>3.69</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.58</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>4.25</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>5.01</v>
+        <v>2.57</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB52" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,22 +6692,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>4.08</v>
+        <v>3.69</v>
       </c>
       <c r="M57" t="n">
-        <v>3.65</v>
+        <v>4.17</v>
       </c>
       <c r="N57" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.04</v>
+        <v>4.08</v>
       </c>
       <c r="M59" t="n">
-        <v>3.37</v>
+        <v>3.65</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>1.74</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,22 +8596,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8628,17 +8628,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M112" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N112" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.41</v>
+        <v>5.28</v>
       </c>
       <c r="M114" t="n">
-        <v>5.23</v>
+        <v>4.67</v>
       </c>
       <c r="N114" t="n">
-        <v>8.6</v>
+        <v>1.64</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.17</v>
+        <v>2.51</v>
       </c>
       <c r="M121" t="n">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="N121" t="n">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>12</v>
+        <v>1.37</v>
       </c>
       <c r="M130" t="n">
-        <v>6.1</v>
+        <v>4.56</v>
       </c>
       <c r="N130" t="n">
-        <v>1.22</v>
+        <v>6.47</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="M138" t="n">
-        <v>4.3</v>
+        <v>3.24</v>
       </c>
       <c r="N138" t="n">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>10.6</v>
+        <v>4.3</v>
       </c>
       <c r="M143" t="n">
-        <v>5.05</v>
+        <v>4.3</v>
       </c>
       <c r="N143" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.61</v>
+        <v>12</v>
       </c>
       <c r="M156" t="n">
-        <v>3.24</v>
+        <v>6.1</v>
       </c>
       <c r="N156" t="n">
-        <v>2.47</v>
+        <v>1.22</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.76</v>
+        <v>2.17</v>
       </c>
       <c r="M159" t="n">
-        <v>3.88</v>
+        <v>3.48</v>
       </c>
       <c r="N159" t="n">
-        <v>4.17</v>
+        <v>3.13</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="M164" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="N164" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB188" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25375,22 +25375,22 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="M213" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="N213" t="n">
-        <v>2.01</v>
+        <v>3.74</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,22 +25970,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="M218" t="n">
-        <v>5.68</v>
+        <v>3.72</v>
       </c>
       <c r="N218" t="n">
-        <v>14.2</v>
+        <v>3.6</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>3.01</v>
+        <v>1.3</v>
       </c>
       <c r="M223" t="n">
-        <v>3.26</v>
+        <v>5.68</v>
       </c>
       <c r="N223" t="n">
-        <v>2.66</v>
+        <v>14.2</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.13</v>
+        <v>5.34</v>
       </c>
       <c r="M225" t="n">
-        <v>3.72</v>
+        <v>3.38</v>
       </c>
       <c r="N225" t="n">
-        <v>3.6</v>
+        <v>1.71</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="M229" t="n">
-        <v>3.31</v>
+        <v>2.97</v>
       </c>
       <c r="N229" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB229" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N238" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N260" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31406,10 +31406,10 @@
         <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB260" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB261" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31920,22 +31920,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32126,10 +32126,10 @@
         <v>0</v>
       </c>
       <c r="AC266" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD266" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE266" t="n">
         <v>0</v>
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32277,22 +32277,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32364,10 +32364,10 @@
         <v>0</v>
       </c>
       <c r="AC268" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD268" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE268" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N281" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33899,10 +33899,10 @@
         <v>0</v>
       </c>
       <c r="Y281" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z281" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34062,7 +34062,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M284" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="N284" t="n">
-        <v>3.57</v>
+        <v>4.76</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,10 +34256,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M285" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N285" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M289" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB289" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L292" t="n">
@@ -35252,7 +35252,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -35262,12 +35262,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,22 +35490,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35604,12 +35604,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35714,7 +35714,7 @@
         <v>0</v>
       </c>
       <c r="AI296" s="3" t="n">
-        <v>46095.875</v>
+        <v>46095.89583333334</v>
       </c>
     </row>
     <row r="297">
@@ -35723,27 +35723,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35833,7 +35833,7 @@
         <v>0</v>
       </c>
       <c r="AI297" s="3" t="n">
-        <v>46095.875</v>
+        <v>46095.89583333334</v>
       </c>
     </row>
     <row r="298">
@@ -35842,27 +35842,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35879,7 +35879,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -35952,7 +35952,7 @@
         <v>0</v>
       </c>
       <c r="AI298" s="3" t="n">
-        <v>46095.875</v>
+        <v>46095.89583333334</v>
       </c>
     </row>
     <row r="299">
@@ -35961,27 +35961,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -36071,7 +36071,7 @@
         <v>0</v>
       </c>
       <c r="AI299" s="3" t="n">
-        <v>46095.875</v>
+        <v>46095.90625</v>
       </c>
     </row>
     <row r="300">
@@ -36080,7 +36080,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36190,7 +36190,7 @@
         <v>0</v>
       </c>
       <c r="AI300" s="3" t="n">
-        <v>46095.89583333334</v>
+        <v>46095.9375</v>
       </c>
     </row>
     <row r="301">
@@ -36199,7 +36199,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36309,7 +36309,7 @@
         <v>0</v>
       </c>
       <c r="AI301" s="3" t="n">
-        <v>46095.89583333334</v>
+        <v>46095.9375</v>
       </c>
     </row>
     <row r="302">
@@ -36318,12 +36318,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36428,7 +36428,7 @@
         <v>0</v>
       </c>
       <c r="AI302" s="3" t="n">
-        <v>46095.89583333334</v>
+        <v>46095.95833333334</v>
       </c>
     </row>
     <row r="303">
@@ -36437,12 +36437,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36547,7 +36547,7 @@
         <v>0</v>
       </c>
       <c r="AI303" s="3" t="n">
-        <v>46095.90625</v>
+        <v>46095.95833333334</v>
       </c>
     </row>
     <row r="304">
@@ -36556,12 +36556,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36666,7 +36666,7 @@
         <v>0</v>
       </c>
       <c r="AI304" s="3" t="n">
-        <v>46095.9375</v>
+        <v>46095.95833333334</v>
       </c>
     </row>
     <row r="305">
@@ -36675,12 +36675,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -36785,7 +36785,7 @@
         <v>0</v>
       </c>
       <c r="AI305" s="3" t="n">
-        <v>46095.9375</v>
+        <v>46095.95833333334</v>
       </c>
     </row>
     <row r="306">
@@ -36794,12 +36794,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -36809,12 +36809,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -36904,482 +36904,6 @@
         <v>0</v>
       </c>
       <c r="AI306" s="3" t="n">
-        <v>46095.95833333334</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>Phoenix Rising</t>
-        </is>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Orange County SC</t>
-        </is>
-      </c>
-      <c r="G307" t="n">
-        <v>0</v>
-      </c>
-      <c r="H307" t="n">
-        <v>0</v>
-      </c>
-      <c r="I307" t="n">
-        <v>0</v>
-      </c>
-      <c r="J307" t="n">
-        <v>0</v>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L307" t="n">
-        <v>0</v>
-      </c>
-      <c r="M307" t="n">
-        <v>0</v>
-      </c>
-      <c r="N307" t="n">
-        <v>0</v>
-      </c>
-      <c r="O307" t="n">
-        <v>0</v>
-      </c>
-      <c r="P307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
-      <c r="R307" t="n">
-        <v>0</v>
-      </c>
-      <c r="S307" t="n">
-        <v>0</v>
-      </c>
-      <c r="T307" t="n">
-        <v>0</v>
-      </c>
-      <c r="U307" t="n">
-        <v>0</v>
-      </c>
-      <c r="V307" t="n">
-        <v>0</v>
-      </c>
-      <c r="W307" t="n">
-        <v>0</v>
-      </c>
-      <c r="X307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y307" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH307" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI307" s="3" t="n">
-        <v>46095.95833333334</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>Tacoma Defiance</t>
-        </is>
-      </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes II</t>
-        </is>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-      <c r="H308" t="n">
-        <v>0</v>
-      </c>
-      <c r="I308" t="n">
-        <v>0</v>
-      </c>
-      <c r="J308" t="n">
-        <v>0</v>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L308" t="n">
-        <v>0</v>
-      </c>
-      <c r="M308" t="n">
-        <v>0</v>
-      </c>
-      <c r="N308" t="n">
-        <v>0</v>
-      </c>
-      <c r="O308" t="n">
-        <v>0</v>
-      </c>
-      <c r="P308" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
-      <c r="R308" t="n">
-        <v>0</v>
-      </c>
-      <c r="S308" t="n">
-        <v>0</v>
-      </c>
-      <c r="T308" t="n">
-        <v>0</v>
-      </c>
-      <c r="U308" t="n">
-        <v>0</v>
-      </c>
-      <c r="V308" t="n">
-        <v>0</v>
-      </c>
-      <c r="W308" t="n">
-        <v>0</v>
-      </c>
-      <c r="X308" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y308" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH308" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI308" s="3" t="n">
-        <v>46095.95833333334</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>Monterey Bay</t>
-        </is>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
-      <c r="H309" t="n">
-        <v>0</v>
-      </c>
-      <c r="I309" t="n">
-        <v>0</v>
-      </c>
-      <c r="J309" t="n">
-        <v>0</v>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L309" t="n">
-        <v>0</v>
-      </c>
-      <c r="M309" t="n">
-        <v>0</v>
-      </c>
-      <c r="N309" t="n">
-        <v>0</v>
-      </c>
-      <c r="O309" t="n">
-        <v>0</v>
-      </c>
-      <c r="P309" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
-      <c r="R309" t="n">
-        <v>0</v>
-      </c>
-      <c r="S309" t="n">
-        <v>0</v>
-      </c>
-      <c r="T309" t="n">
-        <v>0</v>
-      </c>
-      <c r="U309" t="n">
-        <v>0</v>
-      </c>
-      <c r="V309" t="n">
-        <v>0</v>
-      </c>
-      <c r="W309" t="n">
-        <v>0</v>
-      </c>
-      <c r="X309" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y309" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH309" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI309" s="3" t="n">
-        <v>46095.95833333334</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" s="2" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>St. Louis City</t>
-        </is>
-      </c>
-      <c r="G310" t="n">
-        <v>0</v>
-      </c>
-      <c r="H310" t="n">
-        <v>0</v>
-      </c>
-      <c r="I310" t="n">
-        <v>0</v>
-      </c>
-      <c r="J310" t="n">
-        <v>0</v>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L310" t="n">
-        <v>0</v>
-      </c>
-      <c r="M310" t="n">
-        <v>0</v>
-      </c>
-      <c r="N310" t="n">
-        <v>0</v>
-      </c>
-      <c r="O310" t="n">
-        <v>0</v>
-      </c>
-      <c r="P310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
-      <c r="R310" t="n">
-        <v>0</v>
-      </c>
-      <c r="S310" t="n">
-        <v>0</v>
-      </c>
-      <c r="T310" t="n">
-        <v>0</v>
-      </c>
-      <c r="U310" t="n">
-        <v>0</v>
-      </c>
-      <c r="V310" t="n">
-        <v>0</v>
-      </c>
-      <c r="W310" t="n">
-        <v>0</v>
-      </c>
-      <c r="X310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y310" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH310" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI310" s="3" t="n">
         <v>46095.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,22 +2884,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.36</v>
+        <v>6.28</v>
       </c>
       <c r="M22" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5621,22 +5621,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6059,10 +6059,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N52" t="n">
-        <v>2.57</v>
+        <v>3.69</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="M53" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N53" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,22 +6930,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.69</v>
+        <v>2.04</v>
       </c>
       <c r="M57" t="n">
-        <v>4.17</v>
+        <v>3.37</v>
       </c>
       <c r="N57" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.9</v>
+        <v>2.92</v>
       </c>
       <c r="M66" t="n">
-        <v>5.39</v>
+        <v>3.35</v>
       </c>
       <c r="N66" t="n">
-        <v>1.45</v>
+        <v>2.31</v>
       </c>
       <c r="O66" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,22 +11214,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,22 +11690,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N112" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="M113" t="n">
-        <v>4.55</v>
+        <v>4.17</v>
       </c>
       <c r="N113" t="n">
-        <v>4.85</v>
+        <v>5.18</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M114" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N114" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.72</v>
+        <v>5.28</v>
       </c>
       <c r="M115" t="n">
-        <v>4.17</v>
+        <v>4.67</v>
       </c>
       <c r="N115" t="n">
-        <v>5.18</v>
+        <v>1.64</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.25</v>
+        <v>1.37</v>
       </c>
       <c r="M117" t="n">
-        <v>3.11</v>
+        <v>4.56</v>
       </c>
       <c r="N117" t="n">
-        <v>3.05</v>
+        <v>6.47</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.76</v>
+        <v>2.51</v>
       </c>
       <c r="M131" t="n">
-        <v>3.88</v>
+        <v>3.12</v>
       </c>
       <c r="N131" t="n">
-        <v>4.17</v>
+        <v>2.66</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="M134" t="n">
         <v>3.48</v>
       </c>
       <c r="N134" t="n">
-        <v>3.74</v>
+        <v>3.13</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.61</v>
+        <v>2.22</v>
       </c>
       <c r="M138" t="n">
-        <v>3.24</v>
+        <v>3.64</v>
       </c>
       <c r="N138" t="n">
-        <v>2.47</v>
+        <v>2.93</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.07</v>
+        <v>1.44</v>
       </c>
       <c r="M140" t="n">
-        <v>3.42</v>
+        <v>4.15</v>
       </c>
       <c r="N140" t="n">
-        <v>2.52</v>
+        <v>6.11</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>3.76</v>
+        <v>2.32</v>
       </c>
       <c r="M141" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="N141" t="n">
-        <v>2.07</v>
+        <v>3.22</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB151" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.43</v>
+        <v>2.13</v>
       </c>
       <c r="M152" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="N152" t="n">
-        <v>2.75</v>
+        <v>3.29</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>12</v>
+        <v>2.36</v>
       </c>
       <c r="M156" t="n">
-        <v>6.1</v>
+        <v>2.98</v>
       </c>
       <c r="N156" t="n">
-        <v>1.22</v>
+        <v>2.94</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.49</v>
+        <v>2.43</v>
       </c>
       <c r="M157" t="n">
-        <v>4.4</v>
+        <v>3.36</v>
       </c>
       <c r="N157" t="n">
-        <v>5.91</v>
+        <v>2.75</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="M159" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N159" t="n">
-        <v>3.13</v>
+        <v>2.66</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.48</v>
+        <v>3.25</v>
       </c>
       <c r="M160" t="n">
-        <v>4.2</v>
+        <v>3.32</v>
       </c>
       <c r="N160" t="n">
-        <v>6.51</v>
+        <v>2.18</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.31</v>
+        <v>1.49</v>
       </c>
       <c r="M161" t="n">
-        <v>3.56</v>
+        <v>4.4</v>
       </c>
       <c r="N161" t="n">
-        <v>2.83</v>
+        <v>5.91</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="M162" t="n">
-        <v>3.56</v>
+        <v>4.2</v>
       </c>
       <c r="N162" t="n">
-        <v>3.46</v>
+        <v>6.51</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB187" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>3.86</v>
+        <v>8.56</v>
       </c>
       <c r="M188" t="n">
-        <v>3.74</v>
+        <v>5.18</v>
       </c>
       <c r="N188" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22838,10 +22838,10 @@
         <v>0</v>
       </c>
       <c r="AA188" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB188" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,22 +24185,22 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,22 +25613,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.13</v>
+        <v>1.3</v>
       </c>
       <c r="M218" t="n">
-        <v>3.72</v>
+        <v>5.68</v>
       </c>
       <c r="N218" t="n">
-        <v>3.6</v>
+        <v>14.2</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>5.34</v>
+        <v>3.01</v>
       </c>
       <c r="M225" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N225" t="n">
-        <v>1.71</v>
+        <v>2.66</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>3.01</v>
+        <v>2.13</v>
       </c>
       <c r="M227" t="n">
-        <v>3.26</v>
+        <v>3.72</v>
       </c>
       <c r="N227" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB227" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N229" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB230" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="M231" t="n">
-        <v>3.31</v>
+        <v>2.97</v>
       </c>
       <c r="N231" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28350,7 +28350,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N236" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,22 +28826,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB240" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="M243" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N243" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -29788,12 +29788,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB248" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC248" t="n">
         <v>0</v>
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M249" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30254,7 +30254,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30409,13 +30409,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,22 +31325,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32039,22 +32039,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M266" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32158,7 +32158,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -32168,12 +32168,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N267" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB278" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>4.76</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33780,10 +33780,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z280" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="M284" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N284" t="n">
-        <v>4.76</v>
+        <v>3.84</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,16 +34256,16 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z284" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB284" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,10 +34619,10 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC287" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34744,10 +34744,10 @@
         <v>0</v>
       </c>
       <c r="AC288" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD288" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE288" t="n">
         <v>0</v>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34812,13 +34812,13 @@
         </is>
       </c>
       <c r="L289" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N289" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
         <v>0</v>
@@ -34857,10 +34857,10 @@
         <v>0</v>
       </c>
       <c r="AA289" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB289" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC289" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -34976,10 +34976,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB290" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC290" t="n">
         <v>0</v>
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L292" t="n">
@@ -35252,22 +35252,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35371,7 +35371,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -35381,12 +35381,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L295" t="n">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -36002,13 +36002,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M299" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -36047,10 +36047,10 @@
         <v>0</v>
       </c>
       <c r="AA299" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB299" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC299" t="n">
         <v>0</v>
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36121,13 +36121,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M300" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -36166,10 +36166,10 @@
         <v>0</v>
       </c>
       <c r="AA300" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB300" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC300" t="n">
         <v>0</v>
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36291,10 +36291,10 @@
         <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD301" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE301" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -36835,13 +36835,13 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M306" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -36886,10 +36886,10 @@
         <v>0</v>
       </c>
       <c r="AC306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD306" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE306" t="n">
         <v>0</v>

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.28</v>
+        <v>6.36</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4.38</v>
       </c>
       <c r="N22" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.36</v>
+        <v>6.28</v>
       </c>
       <c r="M23" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.21</v>
+        <v>1.45</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N35" t="n">
-        <v>2.84</v>
+        <v>6.19</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>2.21</v>
       </c>
       <c r="M36" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>6.19</v>
+        <v>2.84</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,22 +5978,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,22 +6335,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.84</v>
+        <v>2.4</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N52" t="n">
-        <v>3.69</v>
+        <v>2.57</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.4</v>
+        <v>4.08</v>
       </c>
       <c r="M53" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N53" t="n">
-        <v>2.57</v>
+        <v>1.74</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.58</v>
+        <v>3.69</v>
       </c>
       <c r="M54" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
       <c r="N54" t="n">
-        <v>5.01</v>
+        <v>1.7</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,22 +7049,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="M57" t="n">
-        <v>3.37</v>
+        <v>3.22</v>
       </c>
       <c r="N57" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7323,13 +7323,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.08</v>
+        <v>2.04</v>
       </c>
       <c r="M59" t="n">
-        <v>3.65</v>
+        <v>3.37</v>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>3.25</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>5.39</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46095.41666666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7680,13 +7680,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,22 +7882,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,73 +7918,73 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI63" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,13 +8037,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="N65" t="n">
-        <v>4.56</v>
+        <v>4.23</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.92</v>
+        <v>1.66</v>
       </c>
       <c r="M66" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>2.31</v>
+        <v>4.56</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="M88" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="N88" t="n">
-        <v>3.49</v>
+        <v>3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11214,22 +11214,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.41</v>
+        <v>5.28</v>
       </c>
       <c r="M114" t="n">
-        <v>5.23</v>
+        <v>4.67</v>
       </c>
       <c r="N114" t="n">
-        <v>8.6</v>
+        <v>1.64</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M115" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N115" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14157,10 +14157,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>10.6</v>
+        <v>1.95</v>
       </c>
       <c r="M116" t="n">
-        <v>5.05</v>
+        <v>3.48</v>
       </c>
       <c r="N116" t="n">
-        <v>1.29</v>
+        <v>3.74</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.37</v>
+        <v>10.6</v>
       </c>
       <c r="M117" t="n">
-        <v>4.56</v>
+        <v>5.05</v>
       </c>
       <c r="N117" t="n">
-        <v>6.47</v>
+        <v>1.29</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,22 +14903,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>4.3</v>
+        <v>1.98</v>
       </c>
       <c r="M122" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="N122" t="n">
-        <v>1.72</v>
+        <v>3.86</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.95</v>
+        <v>2.69</v>
       </c>
       <c r="M127" t="n">
-        <v>3.48</v>
+        <v>3.08</v>
       </c>
       <c r="N127" t="n">
-        <v>3.74</v>
+        <v>2.42</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="M128" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="N128" t="n">
-        <v>4.17</v>
+        <v>2.83</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="M132" t="n">
-        <v>6.1</v>
+        <v>3.88</v>
       </c>
       <c r="N132" t="n">
-        <v>1.22</v>
+        <v>4.17</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.17</v>
+        <v>1.37</v>
       </c>
       <c r="M134" t="n">
-        <v>3.48</v>
+        <v>4.56</v>
       </c>
       <c r="N134" t="n">
-        <v>3.13</v>
+        <v>6.47</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.31</v>
+        <v>2.13</v>
       </c>
       <c r="M137" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="N137" t="n">
-        <v>2.83</v>
+        <v>3.29</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="M138" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="N138" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.25</v>
+        <v>3.9</v>
       </c>
       <c r="M139" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N139" t="n">
-        <v>3.05</v>
+        <v>1.85</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M140" t="n">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="N140" t="n">
-        <v>6.11</v>
+        <v>5.91</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="M141" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="N141" t="n">
-        <v>3.22</v>
+        <v>3.13</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.85</v>
+        <v>1.48</v>
       </c>
       <c r="M142" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="N142" t="n">
-        <v>2.6</v>
+        <v>6.51</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M143" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>3.07</v>
+        <v>2.25</v>
       </c>
       <c r="M151" t="n">
-        <v>3.42</v>
+        <v>3.11</v>
       </c>
       <c r="N151" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18435,10 +18435,10 @@
         <v>0</v>
       </c>
       <c r="AA151" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB151" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.13</v>
+        <v>12</v>
       </c>
       <c r="M152" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="N152" t="n">
-        <v>3.29</v>
+        <v>1.22</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.98</v>
+        <v>2.53</v>
       </c>
       <c r="M153" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="N153" t="n">
-        <v>3.86</v>
+        <v>2.76</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="M154" t="n">
-        <v>3.56</v>
+        <v>3.36</v>
       </c>
       <c r="N154" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.43</v>
+        <v>2.61</v>
       </c>
       <c r="M157" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="N157" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.54</v>
+        <v>2.32</v>
       </c>
       <c r="M159" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N159" t="n">
-        <v>2.66</v>
+        <v>3.22</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.49</v>
+        <v>4.3</v>
       </c>
       <c r="M161" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="N161" t="n">
-        <v>5.91</v>
+        <v>1.72</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.48</v>
+        <v>2.85</v>
       </c>
       <c r="M162" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="N162" t="n">
-        <v>6.51</v>
+        <v>2.6</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>1.86</v>
+        <v>3.07</v>
       </c>
       <c r="M163" t="n">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="N163" t="n">
-        <v>3.81</v>
+        <v>2.52</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB163" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB164" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,17 +21361,17 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,17 +21480,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>8.56</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,17 +21956,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22079,13 +22079,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>8.56</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,22 +23590,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,22 +25018,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="M207" t="n">
-        <v>2.74</v>
+        <v>3.43</v>
       </c>
       <c r="N207" t="n">
-        <v>3.74</v>
+        <v>2.01</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="M208" t="n">
-        <v>4.11</v>
+        <v>3.89</v>
       </c>
       <c r="N208" t="n">
-        <v>8.01</v>
+        <v>3.01</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,22 +25970,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>1.3</v>
+        <v>2.13</v>
       </c>
       <c r="M218" t="n">
-        <v>5.68</v>
+        <v>3.72</v>
       </c>
       <c r="N218" t="n">
-        <v>14.2</v>
+        <v>3.6</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M222" t="n">
-        <v>3.9</v>
+        <v>5.68</v>
       </c>
       <c r="N222" t="n">
-        <v>3.7</v>
+        <v>14.2</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>5.34</v>
+        <v>3.01</v>
       </c>
       <c r="M226" t="n">
-        <v>3.38</v>
+        <v>3.26</v>
       </c>
       <c r="N226" t="n">
-        <v>1.71</v>
+        <v>2.66</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27479,10 +27479,10 @@
         <v>0</v>
       </c>
       <c r="AA227" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB227" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC227" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27791,13 +27791,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -27836,10 +27836,10 @@
         <v>0</v>
       </c>
       <c r="AA230" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB230" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC230" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>2.5</v>
+        <v>3.48</v>
       </c>
       <c r="M231" t="n">
-        <v>2.97</v>
+        <v>3.31</v>
       </c>
       <c r="N231" t="n">
-        <v>3.03</v>
+        <v>2.35</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB231" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,22 +28707,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28826,22 +28826,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.88</v>
+        <v>4.74</v>
       </c>
       <c r="M240" t="n">
-        <v>3.47</v>
+        <v>3.94</v>
       </c>
       <c r="N240" t="n">
-        <v>2.53</v>
+        <v>1.66</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29064,7 +29064,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -29074,12 +29074,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>2.37</v>
+        <v>2.88</v>
       </c>
       <c r="M243" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N243" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29383,10 +29383,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB243" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC243" t="n">
         <v>0</v>
@@ -29421,22 +29421,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,22 +29659,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29814,13 +29814,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -29897,7 +29897,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -29907,12 +29907,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N248" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -29978,10 +29978,10 @@
         <v>0</v>
       </c>
       <c r="AA248" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB248" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC248" t="n">
         <v>0</v>
@@ -30016,22 +30016,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30052,13 +30052,13 @@
         </is>
       </c>
       <c r="L249" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M249" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N249" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O249" t="n">
         <v>0</v>
@@ -30135,22 +30135,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30171,13 +30171,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M253" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>5.5</v>
+        <v>1.44</v>
       </c>
       <c r="M261" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="N261" t="n">
-        <v>1.58</v>
+        <v>6</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31525,10 +31525,10 @@
         <v>0</v>
       </c>
       <c r="AA261" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB261" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC261" t="n">
         <v>0</v>
@@ -31563,7 +31563,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -31573,12 +31573,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB262" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="M264" t="n">
-        <v>4</v>
+        <v>4.53</v>
       </c>
       <c r="N264" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32075,13 +32075,13 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N266" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
         <v>0</v>
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N272" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="M277" t="n">
-        <v>2.6</v>
+        <v>4.14</v>
       </c>
       <c r="N277" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB277" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC277" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="M278" t="n">
-        <v>4.14</v>
+        <v>2.6</v>
       </c>
       <c r="N278" t="n">
-        <v>3.53</v>
+        <v>3.17</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB278" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33705,7 +33705,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -33715,12 +33715,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -33741,13 +33741,13 @@
         </is>
       </c>
       <c r="L280" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N280" t="n">
-        <v>4.76</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
@@ -33780,10 +33780,10 @@
         <v>0</v>
       </c>
       <c r="Y280" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z280" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA280" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="M283" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N283" t="n">
-        <v>3.77</v>
+        <v>4.76</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34137,10 +34137,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M286" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB286" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>1.58</v>
+        <v>3.45</v>
       </c>
       <c r="M287" t="n">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="N287" t="n">
-        <v>6.19</v>
+        <v>2.02</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,16 +34619,16 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB287" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC287" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD287" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE287" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="M288" t="n">
-        <v>4.08</v>
+        <v>3.32</v>
       </c>
       <c r="N288" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,16 +34738,16 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB288" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC288" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD288" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE288" t="n">
         <v>0</v>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -34931,13 +34931,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M290" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="N290" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -34976,10 +34976,10 @@
         <v>0</v>
       </c>
       <c r="AA290" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB290" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC290" t="n">
         <v>0</v>
@@ -35014,7 +35014,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -35024,12 +35024,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35046,7 +35046,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L291" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35490,22 +35490,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L295" t="n">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="M296" t="n">
-        <v>3.6</v>
+        <v>4.32</v>
       </c>
       <c r="N296" t="n">
-        <v>3.38</v>
+        <v>5.14</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB296" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>1.65</v>
+        <v>3.18</v>
       </c>
       <c r="M297" t="n">
-        <v>4.32</v>
+        <v>3.53</v>
       </c>
       <c r="N297" t="n">
-        <v>5.14</v>
+        <v>2.16</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB297" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>3.18</v>
+        <v>2.05</v>
       </c>
       <c r="M298" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="N298" t="n">
-        <v>2.16</v>
+        <v>3.38</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36121,13 +36121,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="M300" t="n">
-        <v>3.64</v>
+        <v>4.88</v>
       </c>
       <c r="N300" t="n">
-        <v>3.14</v>
+        <v>5.29</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -36166,16 +36166,16 @@
         <v>0</v>
       </c>
       <c r="AA300" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB300" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC300" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD300" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE300" t="n">
         <v>0</v>
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="M301" t="n">
-        <v>4.88</v>
+        <v>3.64</v>
       </c>
       <c r="N301" t="n">
-        <v>5.29</v>
+        <v>3.14</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36285,16 +36285,16 @@
         <v>0</v>
       </c>
       <c r="AA301" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB301" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC301" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD301" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE301" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36680,7 +36680,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G305" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,22 +980,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>2.21</v>
       </c>
       <c r="M35" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6.19</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="M50" t="n">
-        <v>4.25</v>
+        <v>3.37</v>
       </c>
       <c r="N50" t="n">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,22 +6454,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>3.69</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>4.17</v>
       </c>
       <c r="N52" t="n">
-        <v>2.57</v>
+        <v>1.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>4.08</v>
+        <v>1.84</v>
       </c>
       <c r="M53" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="N53" t="n">
-        <v>1.74</v>
+        <v>3.69</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="M56" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="N56" t="n">
-        <v>3.69</v>
+        <v>3.03</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="M59" t="n">
-        <v>3.37</v>
+        <v>3.25</v>
       </c>
       <c r="N59" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7525,22 +7525,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7561,73 +7561,73 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>5.39</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI60" s="3" t="n">
         <v>46095.41666666666</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="M65" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>4.23</v>
+        <v>4.56</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.66</v>
+        <v>5.9</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>5.39</v>
       </c>
       <c r="N66" t="n">
-        <v>4.56</v>
+        <v>1.45</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="M78" t="n">
-        <v>3.35</v>
+        <v>2.63</v>
       </c>
       <c r="N78" t="n">
-        <v>3.49</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,22 +12047,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Pulau Pinang</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Kuching FA</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Pulau Pinang</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kuching FA</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="M113" t="n">
-        <v>4.17</v>
+        <v>5.23</v>
       </c>
       <c r="N113" t="n">
-        <v>5.18</v>
+        <v>8.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,16 +13913,16 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="M115" t="n">
-        <v>5.23</v>
+        <v>4.17</v>
       </c>
       <c r="N115" t="n">
-        <v>8.6</v>
+        <v>5.18</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,16 +14151,16 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC115" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.95</v>
+        <v>2.51</v>
       </c>
       <c r="M116" t="n">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="N116" t="n">
-        <v>3.74</v>
+        <v>2.66</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>10.6</v>
+        <v>2.17</v>
       </c>
       <c r="M117" t="n">
-        <v>5.05</v>
+        <v>3.48</v>
       </c>
       <c r="N117" t="n">
-        <v>1.29</v>
+        <v>3.13</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>6.47</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="M122" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N122" t="n">
-        <v>3.86</v>
+        <v>3.46</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.25</v>
+        <v>3.76</v>
       </c>
       <c r="M123" t="n">
-        <v>3.32</v>
+        <v>3.76</v>
       </c>
       <c r="N123" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="M124" t="n">
-        <v>3.74</v>
+        <v>3.11</v>
       </c>
       <c r="N124" t="n">
-        <v>3.81</v>
+        <v>3.05</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="M126" t="n">
-        <v>4.15</v>
+        <v>3.88</v>
       </c>
       <c r="N126" t="n">
-        <v>6.11</v>
+        <v>4.17</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.69</v>
+        <v>12</v>
       </c>
       <c r="M127" t="n">
-        <v>3.08</v>
+        <v>6.1</v>
       </c>
       <c r="N127" t="n">
-        <v>2.42</v>
+        <v>1.22</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.31</v>
+        <v>2.61</v>
       </c>
       <c r="M128" t="n">
-        <v>3.56</v>
+        <v>3.24</v>
       </c>
       <c r="N128" t="n">
-        <v>2.83</v>
+        <v>2.47</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.38</v>
+        <v>4.3</v>
       </c>
       <c r="M138" t="n">
-        <v>3.56</v>
+        <v>4.3</v>
       </c>
       <c r="N138" t="n">
-        <v>2.7</v>
+        <v>1.72</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.9</v>
+        <v>1.48</v>
       </c>
       <c r="M139" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="N139" t="n">
-        <v>1.85</v>
+        <v>6.51</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="M141" t="n">
-        <v>3.48</v>
+        <v>3.36</v>
       </c>
       <c r="N141" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.48</v>
+        <v>2.36</v>
       </c>
       <c r="M142" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="N142" t="n">
-        <v>6.51</v>
+        <v>2.94</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.54</v>
+        <v>2.69</v>
       </c>
       <c r="M143" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="N143" t="n">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.22</v>
+        <v>1.44</v>
       </c>
       <c r="M144" t="n">
-        <v>3.64</v>
+        <v>4.15</v>
       </c>
       <c r="N144" t="n">
-        <v>2.93</v>
+        <v>6.11</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.51</v>
+        <v>2.22</v>
       </c>
       <c r="M146" t="n">
-        <v>3.12</v>
+        <v>3.64</v>
       </c>
       <c r="N146" t="n">
-        <v>2.66</v>
+        <v>2.93</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="M151" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="N151" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>12</v>
+        <v>2.38</v>
       </c>
       <c r="M152" t="n">
-        <v>6.1</v>
+        <v>3.48</v>
       </c>
       <c r="N152" t="n">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="M154" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N154" t="n">
-        <v>2.75</v>
+        <v>3.86</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,10 +18792,10 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="M157" t="n">
-        <v>3.24</v>
+        <v>3.56</v>
       </c>
       <c r="N157" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,22 +19544,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>4.3</v>
+        <v>2.53</v>
       </c>
       <c r="M161" t="n">
-        <v>4.3</v>
+        <v>3.18</v>
       </c>
       <c r="N161" t="n">
-        <v>1.72</v>
+        <v>2.76</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.85</v>
+        <v>2.32</v>
       </c>
       <c r="M162" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N162" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19818,13 +19818,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N163" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -19863,10 +19863,10 @@
         <v>0</v>
       </c>
       <c r="AA163" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB163" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC163" t="n">
         <v>0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N164" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -19982,10 +19982,10 @@
         <v>0</v>
       </c>
       <c r="AA164" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB164" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC164" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8.56</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.78</v>
+        <v>3.62</v>
       </c>
       <c r="M180" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="N180" t="n">
-        <v>3.76</v>
+        <v>2.15</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,17 +21956,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>8.56</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,17 +22075,17 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N182" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,22 +23471,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>3.4</v>
+        <v>1.43</v>
       </c>
       <c r="M207" t="n">
-        <v>3.43</v>
+        <v>4.11</v>
       </c>
       <c r="N207" t="n">
-        <v>2.01</v>
+        <v>8.01</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>8.01</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25494,22 +25494,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25851,22 +25851,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26408,10 +26408,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB218" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="M219" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N219" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>14.2</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -27646,12 +27646,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -27672,13 +27672,13 @@
         </is>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O229" t="n">
         <v>0</v>
@@ -27717,10 +27717,10 @@
         <v>0</v>
       </c>
       <c r="AA229" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB229" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC229" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N231" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="AA231" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB231" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC231" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28469,7 +28469,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -28479,12 +28479,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -28505,13 +28505,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -28717,12 +28717,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,22 +28826,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>3.1</v>
+        <v>2.37</v>
       </c>
       <c r="M239" t="n">
-        <v>2.9</v>
+        <v>3.45</v>
       </c>
       <c r="N239" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,7 +28945,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -28955,12 +28955,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB240" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29064,22 +29064,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -29100,13 +29100,13 @@
         </is>
       </c>
       <c r="L241" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N241" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
         <v>0</v>
@@ -29183,7 +29183,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -29193,12 +29193,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29264,10 +29264,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB242" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC242" t="n">
         <v>0</v>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -29431,12 +29431,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -29540,22 +29540,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -29576,13 +29576,13 @@
         </is>
       </c>
       <c r="L245" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N245" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>2.37</v>
+        <v>1.51</v>
       </c>
       <c r="M246" t="n">
-        <v>3.45</v>
+        <v>4.73</v>
       </c>
       <c r="N246" t="n">
-        <v>2.65</v>
+        <v>5.91</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -30026,12 +30026,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30254,22 +30254,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -30290,13 +30290,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -30492,7 +30492,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -30502,12 +30502,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -30528,13 +30528,13 @@
         </is>
       </c>
       <c r="L253" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M253" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N253" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
         <v>0</v>
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M254" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31325,7 +31325,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -31335,12 +31335,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -31361,13 +31361,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M260" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -31444,22 +31444,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>1.44</v>
+        <v>5.03</v>
       </c>
       <c r="M261" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="N261" t="n">
-        <v>6</v>
+        <v>1.67</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31531,10 +31531,10 @@
         <v>0</v>
       </c>
       <c r="AC261" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD261" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE261" t="n">
         <v>0</v>
@@ -31563,22 +31563,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -31599,13 +31599,13 @@
         </is>
       </c>
       <c r="L262" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="N262" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
         <v>0</v>
@@ -31644,10 +31644,10 @@
         <v>0</v>
       </c>
       <c r="AA262" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB262" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC262" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,7 +31801,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -31811,12 +31811,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31837,13 +31837,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -32039,7 +32039,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -32049,12 +32049,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -32158,22 +32158,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -32194,13 +32194,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="M267" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="N267" t="n">
-        <v>6.55</v>
+        <v>5.5</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -32277,7 +32277,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -32287,12 +32287,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -32313,13 +32313,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>5.03</v>
+        <v>5.5</v>
       </c>
       <c r="M268" t="n">
-        <v>4.62</v>
+        <v>3.96</v>
       </c>
       <c r="N268" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -32358,16 +32358,16 @@
         <v>0</v>
       </c>
       <c r="AA268" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB268" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC268" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD268" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE268" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB276" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33348,7 +33348,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -33358,12 +33358,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -33384,13 +33384,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="M277" t="n">
-        <v>4.14</v>
+        <v>2.6</v>
       </c>
       <c r="N277" t="n">
-        <v>3.53</v>
+        <v>3.17</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -33429,10 +33429,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB277" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC277" t="n">
         <v>0</v>
@@ -33467,7 +33467,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -33477,12 +33477,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>2.52</v>
+        <v>1.98</v>
       </c>
       <c r="M278" t="n">
-        <v>2.6</v>
+        <v>4.14</v>
       </c>
       <c r="N278" t="n">
-        <v>3.17</v>
+        <v>3.53</v>
       </c>
       <c r="O278" t="n">
         <v>0</v>
@@ -33548,10 +33548,10 @@
         <v>0</v>
       </c>
       <c r="AA278" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB278" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC278" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="M281" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="N281" t="n">
-        <v>3.77</v>
+        <v>3.84</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33905,10 +33905,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB281" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC281" t="n">
         <v>0</v>
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M282" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="N282" t="n">
-        <v>3.57</v>
+        <v>4.76</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,10 +34018,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -34072,12 +34072,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -34098,13 +34098,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>1.87</v>
+        <v>2.12</v>
       </c>
       <c r="M283" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="N283" t="n">
-        <v>4.76</v>
+        <v>3.77</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -34137,10 +34137,10 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z283" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA283" t="n">
         <v>0</v>
@@ -34181,7 +34181,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="M284" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N284" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34262,10 +34262,10 @@
         <v>0</v>
       </c>
       <c r="AA284" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB284" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB285" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34455,13 +34455,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -34500,10 +34500,10 @@
         <v>0</v>
       </c>
       <c r="AA286" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB286" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC286" t="n">
         <v>0</v>
@@ -34657,7 +34657,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>3.76</v>
+        <v>1.58</v>
       </c>
       <c r="M288" t="n">
-        <v>3.32</v>
+        <v>4.22</v>
       </c>
       <c r="N288" t="n">
-        <v>2.11</v>
+        <v>6.19</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,10 +34738,10 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AB288" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AC288" t="n">
         <v>0</v>
@@ -34776,7 +34776,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -34786,12 +34786,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,22 +35014,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35046,7 +35046,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L291" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -35143,12 +35143,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L292" t="n">
@@ -35252,22 +35252,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35371,22 +35371,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,22 +35490,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35619,12 +35619,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -35645,13 +35645,13 @@
         </is>
       </c>
       <c r="L296" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="M296" t="n">
-        <v>4.32</v>
+        <v>3.6</v>
       </c>
       <c r="N296" t="n">
-        <v>5.14</v>
+        <v>3.38</v>
       </c>
       <c r="O296" t="n">
         <v>0</v>
@@ -35690,10 +35690,10 @@
         <v>0</v>
       </c>
       <c r="AA296" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB296" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC296" t="n">
         <v>0</v>
@@ -35738,12 +35738,12 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -35764,13 +35764,13 @@
         </is>
       </c>
       <c r="L297" t="n">
-        <v>3.18</v>
+        <v>1.65</v>
       </c>
       <c r="M297" t="n">
-        <v>3.53</v>
+        <v>4.32</v>
       </c>
       <c r="N297" t="n">
-        <v>2.16</v>
+        <v>5.14</v>
       </c>
       <c r="O297" t="n">
         <v>0</v>
@@ -35809,10 +35809,10 @@
         <v>0</v>
       </c>
       <c r="AA297" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB297" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC297" t="n">
         <v>0</v>
@@ -35857,12 +35857,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -35883,13 +35883,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>2.05</v>
+        <v>3.18</v>
       </c>
       <c r="M298" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N298" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -36323,7 +36323,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -36333,12 +36333,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -36442,7 +36442,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -36690,12 +36690,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G305" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -742,22 +742,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5026,22 +5026,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,22 +5145,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,22 +5740,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N52" t="n">
         <v>3.69</v>
-      </c>
-      <c r="M52" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="N52" t="n">
-        <v>1.7</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.84</v>
+        <v>3.69</v>
       </c>
       <c r="M53" t="n">
-        <v>3.95</v>
+        <v>4.17</v>
       </c>
       <c r="N53" t="n">
-        <v>3.69</v>
+        <v>1.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7168,22 +7168,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,22 +7287,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="M112" t="n">
-        <v>4.55</v>
+        <v>5.23</v>
       </c>
       <c r="N112" t="n">
-        <v>4.85</v>
+        <v>8.6</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N113" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.51</v>
+        <v>2.17</v>
       </c>
       <c r="M116" t="n">
-        <v>3.12</v>
+        <v>3.48</v>
       </c>
       <c r="N116" t="n">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14270,10 +14270,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.17</v>
+        <v>1.37</v>
       </c>
       <c r="M117" t="n">
-        <v>3.48</v>
+        <v>4.56</v>
       </c>
       <c r="N117" t="n">
-        <v>3.13</v>
+        <v>6.47</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>6.47</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="M121" t="n">
-        <v>3.34</v>
+        <v>3.11</v>
       </c>
       <c r="N121" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.01</v>
+        <v>3.76</v>
       </c>
       <c r="M122" t="n">
-        <v>3.56</v>
+        <v>3.76</v>
       </c>
       <c r="N122" t="n">
-        <v>3.46</v>
+        <v>2.07</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>3.76</v>
+        <v>1.95</v>
       </c>
       <c r="M123" t="n">
-        <v>3.76</v>
+        <v>3.48</v>
       </c>
       <c r="N123" t="n">
-        <v>2.07</v>
+        <v>3.74</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="M125" t="n">
-        <v>3.48</v>
+        <v>3.88</v>
       </c>
       <c r="N125" t="n">
-        <v>3.74</v>
+        <v>4.17</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.76</v>
+        <v>2.61</v>
       </c>
       <c r="M126" t="n">
-        <v>3.88</v>
+        <v>3.24</v>
       </c>
       <c r="N126" t="n">
-        <v>4.17</v>
+        <v>2.47</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,22 +16807,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.3</v>
+        <v>2.85</v>
       </c>
       <c r="M138" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="N138" t="n">
-        <v>1.72</v>
+        <v>2.6</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="M155" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N155" t="n">
-        <v>3.29</v>
+        <v>3.86</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,10 +18911,10 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="M158" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="N158" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.53</v>
+        <v>2.32</v>
       </c>
       <c r="M161" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="N161" t="n">
-        <v>2.76</v>
+        <v>3.22</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="M162" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N162" t="n">
-        <v>3.22</v>
+        <v>1.72</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,17 +21361,17 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,17 +21480,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21603,13 +21603,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>8.56</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="N181" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB185" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3.86</v>
+        <v>8.56</v>
       </c>
       <c r="M189" t="n">
-        <v>3.74</v>
+        <v>5.18</v>
       </c>
       <c r="N189" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,22 +23352,22 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,22 +23471,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23590,7 +23590,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,22 +24304,22 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>3.4</v>
+        <v>2.18</v>
       </c>
       <c r="M201" t="n">
-        <v>3.43</v>
+        <v>3.89</v>
       </c>
       <c r="N201" t="n">
-        <v>2.01</v>
+        <v>3.01</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -24433,12 +24433,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -24459,13 +24459,13 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M202" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="O202" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,22 +24780,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="M205" t="n">
-        <v>3.89</v>
+        <v>3.43</v>
       </c>
       <c r="N205" t="n">
-        <v>3.01</v>
+        <v>2.01</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,22 +24899,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -25137,22 +25137,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,22 +25732,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,22 +25851,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M214" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="N214" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>12.1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26327,7 +26327,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -26337,12 +26337,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -26363,13 +26363,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="M221" t="n">
-        <v>3.9</v>
+        <v>3.72</v>
       </c>
       <c r="N221" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -27279,7 +27279,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -27289,12 +27289,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -27315,13 +27315,13 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>5.34</v>
       </c>
       <c r="M226" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N226" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -27408,12 +27408,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>5.34</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27910,13 +27910,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28029,13 +28029,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N232" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28267,13 +28267,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -28360,12 +28360,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -28386,13 +28386,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N235" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -28588,7 +28588,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -28598,12 +28598,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -28707,22 +28707,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -28743,13 +28743,13 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="M238" t="n">
-        <v>3.15</v>
+        <v>4.73</v>
       </c>
       <c r="N238" t="n">
-        <v>4.42</v>
+        <v>5.91</v>
       </c>
       <c r="O238" t="n">
         <v>0</v>
@@ -28826,7 +28826,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -28836,12 +28836,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -28862,13 +28862,13 @@
         </is>
       </c>
       <c r="L239" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N239" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O239" t="n">
         <v>0</v>
@@ -28945,22 +28945,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -28981,13 +28981,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -29026,10 +29026,10 @@
         <v>0</v>
       </c>
       <c r="AA240" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB240" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC240" t="n">
         <v>0</v>
@@ -29183,22 +29183,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -29219,13 +29219,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>4.74</v>
+        <v>1.8</v>
       </c>
       <c r="M242" t="n">
-        <v>3.94</v>
+        <v>3.15</v>
       </c>
       <c r="N242" t="n">
-        <v>1.66</v>
+        <v>4.42</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -29264,10 +29264,10 @@
         <v>0</v>
       </c>
       <c r="AA242" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB242" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC242" t="n">
         <v>0</v>
@@ -29302,22 +29302,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -29338,13 +29338,13 @@
         </is>
       </c>
       <c r="L243" t="n">
-        <v>2.88</v>
+        <v>4.74</v>
       </c>
       <c r="M243" t="n">
-        <v>3.47</v>
+        <v>3.94</v>
       </c>
       <c r="N243" t="n">
-        <v>2.53</v>
+        <v>1.66</v>
       </c>
       <c r="O243" t="n">
         <v>0</v>
@@ -29383,10 +29383,10 @@
         <v>0</v>
       </c>
       <c r="AA243" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AB243" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AC243" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29669,12 +29669,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -29695,13 +29695,13 @@
         </is>
       </c>
       <c r="L246" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>4.73</v>
+        <v>0</v>
       </c>
       <c r="N246" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
         <v>0</v>
@@ -29778,22 +29778,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -29897,22 +29897,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -29933,13 +29933,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -30135,7 +30135,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -30145,12 +30145,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -30611,7 +30611,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -30621,12 +30621,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -30647,13 +30647,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -30730,7 +30730,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -30740,12 +30740,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -30849,7 +30849,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -30859,12 +30859,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -30885,13 +30885,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -30968,7 +30968,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -30978,12 +30978,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -31004,13 +31004,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>5.41</v>
+        <v>4.62</v>
       </c>
       <c r="M257" t="n">
-        <v>3.85</v>
+        <v>4.42</v>
       </c>
       <c r="N257" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -31087,7 +31087,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -31097,12 +31097,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>4.62</v>
+        <v>5.41</v>
       </c>
       <c r="M258" t="n">
-        <v>4.42</v>
+        <v>3.85</v>
       </c>
       <c r="N258" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -31242,13 +31242,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -31293,10 +31293,10 @@
         <v>0</v>
       </c>
       <c r="AC259" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD259" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE259" t="n">
         <v>0</v>
@@ -31444,7 +31444,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -31454,12 +31454,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -31480,13 +31480,13 @@
         </is>
       </c>
       <c r="L261" t="n">
-        <v>5.03</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="N261" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
         <v>0</v>
@@ -31531,10 +31531,10 @@
         <v>0</v>
       </c>
       <c r="AC261" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD261" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE261" t="n">
         <v>0</v>
@@ -31682,22 +31682,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -31718,13 +31718,13 @@
         </is>
       </c>
       <c r="L263" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N263" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
         <v>0</v>
@@ -31801,22 +31801,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -31930,12 +31930,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -31956,13 +31956,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -32634,7 +32634,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -32644,12 +32644,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -32670,13 +32670,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -32763,12 +32763,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -32789,13 +32789,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -32872,7 +32872,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -32882,12 +32882,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -32908,13 +32908,13 @@
         </is>
       </c>
       <c r="L273" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="N273" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O273" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -33001,12 +33001,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -33027,13 +33027,13 @@
         </is>
       </c>
       <c r="L274" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="N274" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
         <v>0</v>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -33120,12 +33120,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -33146,13 +33146,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -33191,10 +33191,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB275" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -33229,7 +33229,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -33239,12 +33239,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -33310,10 +33310,10 @@
         <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -33824,7 +33824,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -33860,13 +33860,13 @@
         </is>
       </c>
       <c r="L281" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="M281" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N281" t="n">
-        <v>3.84</v>
+        <v>3.57</v>
       </c>
       <c r="O281" t="n">
         <v>0</v>
@@ -33905,10 +33905,10 @@
         <v>0</v>
       </c>
       <c r="AA281" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB281" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC281" t="n">
         <v>0</v>
@@ -33943,7 +33943,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -33953,12 +33953,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -33979,13 +33979,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="M282" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N282" t="n">
-        <v>4.76</v>
+        <v>3.84</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -34018,16 +34018,16 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB282" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC282" t="n">
         <v>0</v>
@@ -34191,12 +34191,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -34217,13 +34217,13 @@
         </is>
       </c>
       <c r="L284" t="n">
-        <v>2.23</v>
+        <v>1.87</v>
       </c>
       <c r="M284" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="N284" t="n">
-        <v>3.57</v>
+        <v>4.76</v>
       </c>
       <c r="O284" t="n">
         <v>0</v>
@@ -34256,10 +34256,10 @@
         <v>0</v>
       </c>
       <c r="Y284" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z284" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA284" t="n">
         <v>0</v>
@@ -34300,7 +34300,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -34310,12 +34310,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -34336,13 +34336,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>3.76</v>
+        <v>1.58</v>
       </c>
       <c r="M285" t="n">
-        <v>3.32</v>
+        <v>4.22</v>
       </c>
       <c r="N285" t="n">
-        <v>2.11</v>
+        <v>6.19</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -34381,10 +34381,10 @@
         <v>0</v>
       </c>
       <c r="AA285" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="AB285" t="n">
-        <v>1.68</v>
+        <v>2.25</v>
       </c>
       <c r="AC285" t="n">
         <v>0</v>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -34429,12 +34429,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -34538,7 +34538,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -34548,12 +34548,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -34574,13 +34574,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>3.45</v>
+        <v>3.76</v>
       </c>
       <c r="M287" t="n">
-        <v>4.08</v>
+        <v>3.32</v>
       </c>
       <c r="N287" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -34619,16 +34619,16 @@
         <v>0</v>
       </c>
       <c r="AA287" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB287" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC287" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AD287" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE287" t="n">
         <v>0</v>
@@ -34667,12 +34667,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -34693,13 +34693,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>1.58</v>
+        <v>3.45</v>
       </c>
       <c r="M288" t="n">
-        <v>4.22</v>
+        <v>4.08</v>
       </c>
       <c r="N288" t="n">
-        <v>6.19</v>
+        <v>2.02</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -34738,16 +34738,16 @@
         <v>0</v>
       </c>
       <c r="AA288" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB288" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC288" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD288" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE288" t="n">
         <v>0</v>
@@ -34895,7 +34895,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -34905,12 +34905,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -35014,22 +35014,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -35133,22 +35133,22 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -35165,7 +35165,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L292" t="n">
@@ -35252,22 +35252,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -35371,22 +35371,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -35500,12 +35500,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -35522,7 +35522,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L295" t="n">
@@ -36095,12 +36095,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -36121,13 +36121,13 @@
         </is>
       </c>
       <c r="L300" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="M300" t="n">
-        <v>4.88</v>
+        <v>3.64</v>
       </c>
       <c r="N300" t="n">
-        <v>5.29</v>
+        <v>3.14</v>
       </c>
       <c r="O300" t="n">
         <v>0</v>
@@ -36166,16 +36166,16 @@
         <v>0</v>
       </c>
       <c r="AA300" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB300" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC300" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AD300" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE300" t="n">
         <v>0</v>
@@ -36214,12 +36214,12 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -36240,13 +36240,13 @@
         </is>
       </c>
       <c r="L301" t="n">
-        <v>2.29</v>
+        <v>1.57</v>
       </c>
       <c r="M301" t="n">
-        <v>3.64</v>
+        <v>4.88</v>
       </c>
       <c r="N301" t="n">
-        <v>3.14</v>
+        <v>5.29</v>
       </c>
       <c r="O301" t="n">
         <v>0</v>
@@ -36285,16 +36285,16 @@
         <v>0</v>
       </c>
       <c r="AA301" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB301" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC301" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD301" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE301" t="n">
         <v>0</v>
@@ -36442,7 +36442,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -36452,12 +36452,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -36561,7 +36561,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -36571,12 +36571,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G304" t="n">

--- a/jogos_2026-03-14.xlsx
+++ b/jogos_2026-03-14.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1337,22 +1337,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newcastle Jets FC</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Newcastle Jets FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FK Sochi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.36</v>
+        <v>6.28</v>
       </c>
       <c r="M22" t="n">
-        <v>4.38</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>FK Sochi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>6.28</v>
+        <v>6.36</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>4.38</v>
       </c>
       <c r="N23" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Academico Viseu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Academico Viseu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,22 +4074,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>East Bengal</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,22 +4312,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4550,22 +4550,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4669,22 +4669,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>East Bengal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,22 +5859,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tianjin Teda</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,22 +6097,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Tianjin Teda</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="M50" t="n">
-        <v>3.37</v>
+        <v>3.95</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>3.69</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>4.08</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>4.25</v>
       </c>
       <c r="N51" t="n">
-        <v>1.74</v>
+        <v>5.01</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.84</v>
+        <v>2.34</v>
       </c>
       <c r="M52" t="n">
-        <v>3.95</v>
+        <v>3.22</v>
       </c>
       <c r="N52" t="n">
-        <v>3.69</v>
+        <v>3.03</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="M55" t="n">
-        <v>4.25</v>
+        <v>3.37</v>
       </c>
       <c r="N55" t="n">
-        <v>5.01</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AB55" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.34</v>
+        <v>4.08</v>
       </c>
       <c r="M56" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="N56" t="n">
-        <v>3.03</v>
+        <v>1.74</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7442,13 +7442,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8001,22 +8001,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8037,73 +8037,73 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.92</v>
+        <v>5.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>5.39</v>
       </c>
       <c r="N64" t="n">
-        <v>2.31</v>
+        <v>1.45</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI64" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8156,13 +8156,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,73 +8275,73 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.9</v>
+        <v>1.43</v>
       </c>
       <c r="M66" t="n">
-        <v>5.39</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>1.45</v>
+        <v>6.54</v>
       </c>
       <c r="O66" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI66" s="3" t="n">
         <v>46095.41666666666</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MSV Duisburg</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>MSV Duisburg</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.23</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10857,7 +10857,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Gorica</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,22 +12761,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gorica</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,22 +13594,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M112" t="n">
-        <v>5.23</v>
+        <v>4.55</v>
       </c>
       <c r="N112" t="n">
-        <v>8.6</v>
+        <v>4.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13800,10 +13800,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD112" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>5.28</v>
       </c>
       <c r="M113" t="n">
-        <v>4.55</v>
+        <v>4.67</v>
       </c>
       <c r="N113" t="n">
-        <v>4.85</v>
+        <v>1.64</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13919,10 +13919,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>5.28</v>
+        <v>1.41</v>
       </c>
       <c r="M114" t="n">
-        <v>4.67</v>
+        <v>5.23</v>
       </c>
       <c r="N114" t="n">
-        <v>1.64</v>
+        <v>8.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14038,10 +14038,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -14189,22 +14189,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.17</v>
+        <v>4.3</v>
       </c>
       <c r="M116" t="n">
-        <v>3.48</v>
+        <v>4.3</v>
       </c>
       <c r="N116" t="n">
-        <v>3.13</v>
+        <v>1.72</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.37</v>
+        <v>2.85</v>
       </c>
       <c r="M117" t="n">
-        <v>4.56</v>
+        <v>2.9</v>
       </c>
       <c r="N117" t="n">
-        <v>6.47</v>
+        <v>2.6</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="M119" t="n">
-        <v>3.56</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.25</v>
+        <v>10.6</v>
       </c>
       <c r="M121" t="n">
-        <v>3.11</v>
+        <v>5.05</v>
       </c>
       <c r="N121" t="n">
-        <v>3.05</v>
+        <v>1.29</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.76</v>
+        <v>2.61</v>
       </c>
       <c r="M125" t="n">
-        <v>3.88</v>
+        <v>3.24</v>
       </c>
       <c r="N125" t="n">
-        <v>4.17</v>
+        <v>2.47</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.61</v>
+        <v>3.07</v>
       </c>
       <c r="M126" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="N126" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>12</v>
+        <v>3.76</v>
       </c>
       <c r="M127" t="n">
-        <v>6.1</v>
+        <v>3.76</v>
       </c>
       <c r="N127" t="n">
-        <v>1.22</v>
+        <v>2.07</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.31</v>
+        <v>2.22</v>
       </c>
       <c r="M131" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="N131" t="n">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.51</v>
+        <v>1.49</v>
       </c>
       <c r="M134" t="n">
-        <v>3.12</v>
+        <v>4.4</v>
       </c>
       <c r="N134" t="n">
-        <v>2.66</v>
+        <v>5.91</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>6.51</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="M137" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="N137" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="M138" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="N138" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="M139" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
       <c r="N139" t="n">
-        <v>6.51</v>
+        <v>6.47</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.49</v>
+        <v>12</v>
       </c>
       <c r="M140" t="n">
-        <v>4.4</v>
+        <v>6.1</v>
       </c>
       <c r="N140" t="n">
-        <v>5.91</v>
+        <v>1.22</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="M143" t="n">
-        <v>3.08</v>
+        <v>3.48</v>
       </c>
       <c r="N143" t="n">
-        <v>2.42</v>
+        <v>3.74</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.44</v>
+        <v>3.25</v>
       </c>
       <c r="M144" t="n">
-        <v>4.15</v>
+        <v>3.32</v>
       </c>
       <c r="N144" t="n">
-        <v>6.11</v>
+        <v>2.18</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.22</v>
+        <v>1.98</v>
       </c>
       <c r="M147" t="n">
-        <v>3.64</v>
+        <v>3.3</v>
       </c>
       <c r="N147" t="n">
-        <v>2.93</v>
+        <v>3.86</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.25</v>
+        <v>2.38</v>
       </c>
       <c r="M149" t="n">
-        <v>3.32</v>
+        <v>3.56</v>
       </c>
       <c r="N149" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>2.54</v>
+        <v>2.31</v>
       </c>
       <c r="M150" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N150" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="M152" t="n">
         <v>3.48</v>
       </c>
       <c r="N152" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,10 +18554,10 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,10 +19030,10 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="M158" t="n">
-        <v>3.56</v>
+        <v>3.12</v>
       </c>
       <c r="N158" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,10 +19268,10 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,10 +19387,10 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>10.6</v>
+        <v>1.76</v>
       </c>
       <c r="M160" t="n">
-        <v>5.05</v>
+        <v>3.88</v>
       </c>
       <c r="N160" t="n">
-        <v>1.29</v>
+        <v>4.17</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.32</v>
+        <v>2.53</v>
       </c>
       <c r="M161" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N161" t="n">
-        <v>3.22</v>
+        <v>2.76</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19663,22 +19663,22 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -19937,13 +19937,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21361,17 +21361,17 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21480,17 +21480,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21722,13 +21722,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="M179" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -21767,10 +21767,10 @@
         <v>0</v>
       </c>
       <c r="AA179" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB179" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC179" t="n">
         <v>0</v>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21960,13 +21960,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22432,17 +22432,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22481,10 +22481,10 @@
         <v>0</v>
       </c>
       <c r="AA185" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB185" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>8.56</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
